--- a/results/Int Task Remove ACC -0.7/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.7/Linea_fi_all.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.010605134474327671 +/- 0.002327759660675969</t>
+          <t>-0.010635696821515928 +/- 0.002298483579090835</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.01916838690651721 +/- 0.0035996920128970066</t>
+          <t>0.019197876732527243 +/- 0.0035741133826272245</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.0045119433795341 +/- 0.0043801078843288994</t>
+          <t>-0.00448245355352408 +/- 0.004385564481278981</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>-0.025626658802713122 +/- 0.0034250119220453766</t>
+          <t>-0.02565614862872314 +/- 0.0034817982054014458</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.000503107428233196 +/- 0.0007009600048728498</t>
+          <t>-0.0004735128736312433 +/- 0.0007028317305142174</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.029357798165137616 +/- 0.0036385659400541563</t>
+          <t>0.02938739271973957 +/- 0.0036028863415054095</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.0016543574593796072 +/- 0.002454662106687253</t>
+          <t>0.001683899556868529 +/- 0.002478897098469491</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.008360413589364901 +/- 0.001447562776957173</t>
+          <t>-0.008301329394387057 +/- 0.0014973501799083334</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.004410894020130218 +/- 0.0012451001092251683</t>
+          <t>-0.004381290704558871 +/- 0.0012615320161434313</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>0.027323860272350543 +/- 0.0034012908463510756</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>0.02735346358792188 +/- 0.003373219546061369</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.027323860272350543 +/- 0.0034012908463510756</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.00025070510811658897 +/- 0.0007650614613433832</t>
+          <t>0.0002193669696020084 +/- 0.0007553726601813777</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0015669069257286173 +/- 0.0005945993720153526</t>
+          <t>0.0015982450642431979 +/- 0.000664043249778042</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.0015669069257286284 +/- 0.000672128191461218</t>
+          <t>0.0015982450642431979 +/- 0.000664043249778042</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.07819032761310454 +/- 0.00517827929752879</t>
+          <t>0.07822152886115447 +/- 0.0052005096116385695</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4026,74 +4026,74 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>-0.0014736221632772883 +/- 0.0007908286392572012</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.014382552313586826 +/- 0.005131591647182295</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.03309755378720898 +/- 0.0030516434395240514</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.03309755378720898 +/- 0.0030516434395240514</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.0667256115531978 +/- 0.004834199482183943</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.016681402888299467 +/- 0.002982984009167109</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.006189213085764844 +/- 0.001425686604473654</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>-0.012496315944591751 +/- 0.003767864854582232</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.06318891836133218 +/- 0.0033660575385250214</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.006159740642499278 +/- 0.002428393404670171</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.08063660477453585 +/- 0.005351014072165693</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>-0.002564102564102555 +/- 0.0046749835734321565</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.0029177718832891554 +/- 0.00496232280605028</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>-0.0014441497200117447 +/- 0.0007847643357320394</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.014382552313586826 +/- 0.005131591647182295</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.03309755378720898 +/- 0.0030516434395240514</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.03309755378720898 +/- 0.0030516434395240514</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.0667256115531978 +/- 0.004834199482183943</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.016651930445033925 +/- 0.003017868818015208</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.006189213085764844 +/- 0.001425686604473654</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>-0.012496315944591751 +/- 0.003767864854582232</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0.06318891836133218 +/- 0.0033660575385250214</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0.006100795755968192 +/- 0.0024905522473708396</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0.08063660477453585 +/- 0.005351014072165693</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>-0.002564102564102555 +/- 0.0046749835734321565</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>0.0029177718832891554 +/- 0.00496232280605028</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>-0.0014441497200117447 +/- 0.0007847643357320394</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>-0.05237253168287646 +/- 0.002117303278003147</t>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.00020630710285879372 +/- 0.002887848295964399</t>
+          <t>-0.00023577954612433727 +/- 0.0028780561428196345</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.03558052434456934 +/- 0.0023696231650795945</t>
+          <t>0.03560933448573903 +/- 0.0023694480201615774</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.007433016421780414 +/- 0.0016789170019399118</t>
+          <t>-0.007404206280610726 +/- 0.001685085429661754</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0002881014116969616 +/- 0.0009019000773551459</t>
+          <t>0.0002304811293575626 +/- 0.0008527023098212919</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.02258715067703836 +/- 0.002383418943237873</t>
+          <t>0.022615960818208058 +/- 0.0023661178034488427</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.0002881014116969616 +/- 0.0009019000773551459</t>
+          <t>0.00031691155286664994 +/- 0.0008875207030106256</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.005214635551714275 +/- 0.0006872290660833595</t>
+          <t>0.005214635551714275 +/- 0.0007884720359207123</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.09289113622843544 +/- 0.0033442058831916195</t>
+          <t>0.09286139202855441 +/- 0.003359383201307658</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.0012195121951219744 +/- 0.0013198517389847587</t>
+          <t>-0.0011600237953599325 +/- 0.001306376636287792</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.000832837596668623 +/- 0.0016603552334268714</t>
+          <t>0.000832837596668623 +/- 0.0016171656417689705</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.000832837596668623 +/- 0.0016496638457896534</t>
+          <t>0.000862581796549644 +/- 0.0016261673923660509</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>0.007257584770969638 +/- 0.002300901797241383</t>
+          <t>0.0072873289708506594 +/- 0.0023354406296792005</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
